--- a/artfynd/A 36234-2026 artfynd.xlsx
+++ b/artfynd/A 36234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438019</v>
       </c>
       <c r="B2" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438022</v>
       </c>
       <c r="B3" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438021</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438023</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438020</v>
       </c>
       <c r="B6" t="n">
-        <v>108091</v>
+        <v>108104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36234-2026 artfynd.xlsx
+++ b/artfynd/A 36234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438019</v>
       </c>
       <c r="B2" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438022</v>
       </c>
       <c r="B3" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438021</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438023</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438020</v>
       </c>
       <c r="B6" t="n">
-        <v>108104</v>
+        <v>108105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
